--- a/Deliverables/BOM/Electrode-Board/LCSC_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/LCSC_BOM_Electrode_Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C88631D-3596-4FF5-8D73-96E0434D8931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A7C8E4-6532-40C2-B017-8D2B59E37825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="840" windowWidth="11790" windowHeight="15360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="113">
   <si>
     <t>Component list</t>
   </si>
@@ -1146,8 +1146,17 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1193,17 +1202,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1577,15 +1577,15 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="84"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="87"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1632,8 +1632,8 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="92"/>
+      <c r="Q3" s="94"/>
+      <c r="R3" s="95"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1656,8 +1656,8 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="94"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="97"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1680,8 +1680,8 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
-      <c r="Q5" s="93"/>
-      <c r="R5" s="94"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="97"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1700,8 +1700,8 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="94"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="97"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1720,8 +1720,8 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
-      <c r="Q7" s="93"/>
-      <c r="R7" s="94"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="97"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1740,8 +1740,8 @@
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
-      <c r="Q8" s="95"/>
-      <c r="R8" s="96"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="99"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2557,17 +2557,17 @@
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
       <c r="L24" s="37"/>
-      <c r="M24" s="89" t="s">
+      <c r="M24" s="92" t="s">
         <v>110</v>
       </c>
-      <c r="N24" s="90"/>
-      <c r="O24" s="90"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
       <c r="P24" s="79">
         <f>SUM(P10:P23)</f>
         <v>220.64230000000001</v>
       </c>
-      <c r="Q24" s="85"/>
-      <c r="R24" s="86"/>
+      <c r="Q24" s="88"/>
+      <c r="R24" s="89"/>
     </row>
     <row r="25" spans="1:18" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2584,17 +2584,17 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="89" t="s">
+      <c r="M25" s="92" t="s">
         <v>111</v>
       </c>
-      <c r="N25" s="90"/>
-      <c r="O25" s="90"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
       <c r="P25" s="80">
         <f>P24/5</f>
         <v>44.128460000000004</v>
       </c>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="88"/>
+      <c r="Q25" s="90"/>
+      <c r="R25" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2626,7 +2626,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D987507-D41F-474A-B079-A5BCCAD8AD34}">
-  <dimension ref="B1:D14"/>
+  <dimension ref="B1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -2650,10 +2650,10 @@
       <c r="B3" s="38">
         <v>1</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="52" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="43">
+      <c r="D3" s="53">
         <v>60</v>
       </c>
     </row>
@@ -2661,10 +2661,10 @@
       <c r="B4" s="38">
         <v>2</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="83">
         <v>50</v>
       </c>
     </row>
@@ -2672,10 +2672,10 @@
       <c r="B5" s="38">
         <v>3</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="53">
         <v>100</v>
       </c>
     </row>
@@ -2683,10 +2683,10 @@
       <c r="B6" s="38">
         <v>4</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="82">
+      <c r="D6" s="100">
         <v>50</v>
       </c>
     </row>
@@ -2694,87 +2694,76 @@
       <c r="B7" s="38">
         <v>5</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="84" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="53">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="38">
-        <v>6</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="47">
-        <v>42</v>
+        <v>7</v>
+      </c>
+      <c r="C8" s="82" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="83">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="38">
-        <v>7</v>
-      </c>
-      <c r="C9" s="97" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="98">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="C9" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="53">
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="38">
-        <v>8</v>
-      </c>
-      <c r="C10" s="99" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="53">
-        <v>300</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="83">
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="38">
-        <v>9</v>
-      </c>
-      <c r="C11" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" s="98">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="C11" s="84" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="53">
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="38">
-        <v>10</v>
-      </c>
-      <c r="C12" s="99" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="53">
-        <v>45</v>
+        <v>11</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="83">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="38">
-        <v>11</v>
-      </c>
-      <c r="C13" s="97" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="98">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="38">
         <v>12</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C13" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="100">
+      <c r="D13" s="85">
         <v>42</v>
       </c>
     </row>

--- a/Deliverables/BOM/Electrode-Board/LCSC_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/LCSC_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9194C5A-D20C-4D5D-8049-8F93760F6304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9934645-EE68-4C68-8C19-44BF0646E6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -609,7 +609,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="5">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">

--- a/Deliverables/BOM/Electrode-Board/LCSC_BOM_Electrode_Board.xlsx
+++ b/Deliverables/BOM/Electrode-Board/LCSC_BOM_Electrode_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ManarHarake-sEMGDevice\Deliverables\BOM\Electrode-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9934645-EE68-4C68-8C19-44BF0646E6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78804275-6DB2-4BEE-A6A3-CEC4F4C3328A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>C307331</t>
   </si>
   <si>
-    <t>C2922482</t>
-  </si>
-  <si>
     <t>C325464</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>C110221</t>
+  </si>
+  <si>
+    <t>C91606</t>
   </si>
 </sst>
 </file>
@@ -606,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2" s="5">
         <v>50</v>
@@ -628,7 +628,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5">
         <v>100</v>
@@ -639,7 +639,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="12">
         <v>50</v>
@@ -650,7 +650,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5">
         <v>100</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="9">
         <v>100</v>
@@ -672,7 +672,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="5">
         <v>300</v>
@@ -683,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="9">
         <v>100</v>
@@ -694,7 +694,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5">
         <v>45</v>
@@ -705,7 +705,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9">
         <v>100</v>
@@ -716,7 +716,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="11">
         <v>42</v>
